--- a/templates/受講者一覧_入力テンプレート.xlsx
+++ b/templates/受講者一覧_入力テンプレート.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="受講者一覧" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="入力説明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受講者一覧" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力説明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,10 +37,9 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -49,14 +48,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,26 +71,37 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -454,21 +467,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:P100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
@@ -480,177 +500,252 @@
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>フリガナ</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>メールアドレス
+(eラーニングの場合は必須)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>雇用区分
+(正規雇用/有期契約)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>雇用保険被保険者番号
 (4桁-6桁-1桁)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>雇用形態
-(正規雇用/有期契約)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>所属事業所
+(本社以外の場合)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>受講場所
+(在宅の場合)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>受講場所
+(名称・住所)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>雇用契約書
+チェック</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>カリキュラム名</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>訓練開始日
 (YYYY/MM/DD)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>訓練終了日
 (YYYY/MM/DD)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>受講料(税抜)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>助成コース
 (リスキリング/定額制)</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>山田 太郎</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>ヤマダ タロウ</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>yamada@example.com</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>正規雇用労働者等</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1234-567890-1</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>正規雇用</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>○○営業所(東京都...)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>DX基礎研修</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>2026/05/01</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>2026/07/31</t>
         </is>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="O2" s="2" t="n">
         <v>50000</v>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>リスキリング</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>佐藤 花子</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>サトウ ハナコ</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>sato@example.com</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>正規雇用労働者等</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>2345-678901-2</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>正規雇用</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>大阪支店</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>在宅</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>DX基礎研修</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>2026/05/01</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>2026/07/31</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="O3" s="2" t="n">
         <v>50000</v>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>リスキリング</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>鈴木 一郎</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>3456-789012-3</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>有期契約</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>AI活用研修</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>2026/08/31</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>80000</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>定額制</t>
-        </is>
-      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n"/>
@@ -661,9 +756,16 @@
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="n"/>
@@ -674,9 +776,16 @@
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n"/>
@@ -687,9 +796,16 @@
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="n"/>
@@ -700,9 +816,16 @@
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n"/>
@@ -713,9 +836,16 @@
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="n"/>
@@ -726,9 +856,16 @@
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n"/>
@@ -739,9 +876,16 @@
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -752,9 +896,16 @@
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -765,9 +916,16 @@
       <c r="G13" s="3" t="n"/>
       <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="n"/>
@@ -778,9 +936,16 @@
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="3" t="n"/>
       <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3" t="n"/>
+      <c r="O14" s="3" t="n"/>
+      <c r="P14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n"/>
@@ -791,9 +956,16 @@
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="3" t="n"/>
       <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="n"/>
@@ -804,9 +976,16 @@
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="3" t="n"/>
       <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3" t="n"/>
+      <c r="O16" s="3" t="n"/>
+      <c r="P16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n"/>
@@ -817,9 +996,16 @@
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="n"/>
       <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="n"/>
+      <c r="P17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="n"/>
@@ -830,9 +1016,16 @@
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="3" t="n"/>
       <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
+      <c r="N18" s="3" t="n"/>
+      <c r="O18" s="3" t="n"/>
+      <c r="P18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n"/>
@@ -843,9 +1036,16 @@
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
+      <c r="O19" s="3" t="n"/>
+      <c r="P19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="n"/>
@@ -856,9 +1056,16 @@
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="3" t="n"/>
       <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
+      <c r="N20" s="3" t="n"/>
+      <c r="O20" s="3" t="n"/>
+      <c r="P20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n"/>
@@ -869,9 +1076,16 @@
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n"/>
+      <c r="P21" s="3" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="n"/>
@@ -882,9 +1096,16 @@
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="3" t="n"/>
       <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="n"/>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
+      <c r="N22" s="3" t="n"/>
+      <c r="O22" s="3" t="n"/>
+      <c r="P22" s="3" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n"/>
@@ -895,9 +1116,16 @@
       <c r="G23" s="3" t="n"/>
       <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
+      <c r="O23" s="3" t="n"/>
+      <c r="P23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="n"/>
@@ -908,9 +1136,16 @@
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="n"/>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="n"/>
+      <c r="M24" s="3" t="n"/>
+      <c r="N24" s="3" t="n"/>
+      <c r="O24" s="3" t="n"/>
+      <c r="P24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n"/>
@@ -921,9 +1156,16 @@
       <c r="G25" s="3" t="n"/>
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="3" t="n"/>
+      <c r="O25" s="3" t="n"/>
+      <c r="P25" s="3" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="n"/>
@@ -934,9 +1176,16 @@
       <c r="G26" s="3" t="n"/>
       <c r="H26" s="3" t="n"/>
       <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="3" t="n"/>
+      <c r="M26" s="3" t="n"/>
+      <c r="N26" s="3" t="n"/>
+      <c r="O26" s="3" t="n"/>
+      <c r="P26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n"/>
@@ -947,9 +1196,16 @@
       <c r="G27" s="3" t="n"/>
       <c r="H27" s="3" t="n"/>
       <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3" t="n"/>
+      <c r="O27" s="3" t="n"/>
+      <c r="P27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="n"/>
@@ -960,9 +1216,16 @@
       <c r="G28" s="3" t="n"/>
       <c r="H28" s="3" t="n"/>
       <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="n"/>
+      <c r="M28" s="3" t="n"/>
+      <c r="N28" s="3" t="n"/>
+      <c r="O28" s="3" t="n"/>
+      <c r="P28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n"/>
@@ -973,9 +1236,16 @@
       <c r="G29" s="3" t="n"/>
       <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3" t="n"/>
+      <c r="O29" s="3" t="n"/>
+      <c r="P29" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="n"/>
@@ -986,9 +1256,16 @@
       <c r="G30" s="3" t="n"/>
       <c r="H30" s="3" t="n"/>
       <c r="I30" s="3" t="n"/>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="3" t="n"/>
+      <c r="O30" s="3" t="n"/>
+      <c r="P30" s="3" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n"/>
@@ -999,9 +1276,16 @@
       <c r="G31" s="3" t="n"/>
       <c r="H31" s="3" t="n"/>
       <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3" t="n"/>
+      <c r="O31" s="3" t="n"/>
+      <c r="P31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="n"/>
@@ -1012,9 +1296,16 @@
       <c r="G32" s="3" t="n"/>
       <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="n"/>
+      <c r="M32" s="3" t="n"/>
+      <c r="N32" s="3" t="n"/>
+      <c r="O32" s="3" t="n"/>
+      <c r="P32" s="3" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n"/>
@@ -1025,9 +1316,16 @@
       <c r="G33" s="3" t="n"/>
       <c r="H33" s="3" t="n"/>
       <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3" t="n"/>
+      <c r="O33" s="3" t="n"/>
+      <c r="P33" s="3" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="n"/>
@@ -1038,9 +1336,16 @@
       <c r="G34" s="3" t="n"/>
       <c r="H34" s="3" t="n"/>
       <c r="I34" s="3" t="n"/>
+      <c r="J34" s="3" t="n"/>
+      <c r="K34" s="3" t="n"/>
+      <c r="L34" s="3" t="n"/>
+      <c r="M34" s="3" t="n"/>
+      <c r="N34" s="3" t="n"/>
+      <c r="O34" s="3" t="n"/>
+      <c r="P34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n"/>
@@ -1051,9 +1356,16 @@
       <c r="G35" s="3" t="n"/>
       <c r="H35" s="3" t="n"/>
       <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3" t="n"/>
+      <c r="O35" s="3" t="n"/>
+      <c r="P35" s="3" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="n"/>
@@ -1064,9 +1376,16 @@
       <c r="G36" s="3" t="n"/>
       <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="n"/>
+      <c r="J36" s="3" t="n"/>
+      <c r="K36" s="3" t="n"/>
+      <c r="L36" s="3" t="n"/>
+      <c r="M36" s="3" t="n"/>
+      <c r="N36" s="3" t="n"/>
+      <c r="O36" s="3" t="n"/>
+      <c r="P36" s="3" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n"/>
@@ -1077,9 +1396,16 @@
       <c r="G37" s="3" t="n"/>
       <c r="H37" s="3" t="n"/>
       <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="n"/>
+      <c r="L37" s="3" t="n"/>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
+      <c r="O37" s="3" t="n"/>
+      <c r="P37" s="3" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="n"/>
@@ -1090,9 +1416,16 @@
       <c r="G38" s="3" t="n"/>
       <c r="H38" s="3" t="n"/>
       <c r="I38" s="3" t="n"/>
+      <c r="J38" s="3" t="n"/>
+      <c r="K38" s="3" t="n"/>
+      <c r="L38" s="3" t="n"/>
+      <c r="M38" s="3" t="n"/>
+      <c r="N38" s="3" t="n"/>
+      <c r="O38" s="3" t="n"/>
+      <c r="P38" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n"/>
@@ -1103,9 +1436,16 @@
       <c r="G39" s="3" t="n"/>
       <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="n"/>
+      <c r="O39" s="3" t="n"/>
+      <c r="P39" s="3" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="n"/>
@@ -1116,9 +1456,16 @@
       <c r="G40" s="3" t="n"/>
       <c r="H40" s="3" t="n"/>
       <c r="I40" s="3" t="n"/>
+      <c r="J40" s="3" t="n"/>
+      <c r="K40" s="3" t="n"/>
+      <c r="L40" s="3" t="n"/>
+      <c r="M40" s="3" t="n"/>
+      <c r="N40" s="3" t="n"/>
+      <c r="O40" s="3" t="n"/>
+      <c r="P40" s="3" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="n"/>
@@ -1129,9 +1476,16 @@
       <c r="G41" s="3" t="n"/>
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="n"/>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="n"/>
+      <c r="O41" s="3" t="n"/>
+      <c r="P41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="n"/>
@@ -1142,9 +1496,16 @@
       <c r="G42" s="3" t="n"/>
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n"/>
+      <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="n"/>
+      <c r="L42" s="3" t="n"/>
+      <c r="M42" s="3" t="n"/>
+      <c r="N42" s="3" t="n"/>
+      <c r="O42" s="3" t="n"/>
+      <c r="P42" s="3" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="n"/>
@@ -1155,9 +1516,16 @@
       <c r="G43" s="3" t="n"/>
       <c r="H43" s="3" t="n"/>
       <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="n"/>
+      <c r="L43" s="3" t="n"/>
+      <c r="M43" s="3" t="n"/>
+      <c r="N43" s="3" t="n"/>
+      <c r="O43" s="3" t="n"/>
+      <c r="P43" s="3" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="n"/>
@@ -1168,9 +1536,16 @@
       <c r="G44" s="3" t="n"/>
       <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="n"/>
+      <c r="J44" s="3" t="n"/>
+      <c r="K44" s="3" t="n"/>
+      <c r="L44" s="3" t="n"/>
+      <c r="M44" s="3" t="n"/>
+      <c r="N44" s="3" t="n"/>
+      <c r="O44" s="3" t="n"/>
+      <c r="P44" s="3" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="n"/>
@@ -1181,9 +1556,16 @@
       <c r="G45" s="3" t="n"/>
       <c r="H45" s="3" t="n"/>
       <c r="I45" s="3" t="n"/>
+      <c r="J45" s="3" t="n"/>
+      <c r="K45" s="3" t="n"/>
+      <c r="L45" s="3" t="n"/>
+      <c r="M45" s="3" t="n"/>
+      <c r="N45" s="3" t="n"/>
+      <c r="O45" s="3" t="n"/>
+      <c r="P45" s="3" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="n"/>
@@ -1194,9 +1576,16 @@
       <c r="G46" s="3" t="n"/>
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n"/>
+      <c r="J46" s="3" t="n"/>
+      <c r="K46" s="3" t="n"/>
+      <c r="L46" s="3" t="n"/>
+      <c r="M46" s="3" t="n"/>
+      <c r="N46" s="3" t="n"/>
+      <c r="O46" s="3" t="n"/>
+      <c r="P46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="n"/>
@@ -1207,9 +1596,16 @@
       <c r="G47" s="3" t="n"/>
       <c r="H47" s="3" t="n"/>
       <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="n"/>
+      <c r="L47" s="3" t="n"/>
+      <c r="M47" s="3" t="n"/>
+      <c r="N47" s="3" t="n"/>
+      <c r="O47" s="3" t="n"/>
+      <c r="P47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="n"/>
@@ -1220,9 +1616,16 @@
       <c r="G48" s="3" t="n"/>
       <c r="H48" s="3" t="n"/>
       <c r="I48" s="3" t="n"/>
+      <c r="J48" s="3" t="n"/>
+      <c r="K48" s="3" t="n"/>
+      <c r="L48" s="3" t="n"/>
+      <c r="M48" s="3" t="n"/>
+      <c r="N48" s="3" t="n"/>
+      <c r="O48" s="3" t="n"/>
+      <c r="P48" s="3" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="n"/>
@@ -1233,9 +1636,16 @@
       <c r="G49" s="3" t="n"/>
       <c r="H49" s="3" t="n"/>
       <c r="I49" s="3" t="n"/>
+      <c r="J49" s="3" t="n"/>
+      <c r="K49" s="3" t="n"/>
+      <c r="L49" s="3" t="n"/>
+      <c r="M49" s="3" t="n"/>
+      <c r="N49" s="3" t="n"/>
+      <c r="O49" s="3" t="n"/>
+      <c r="P49" s="3" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="n"/>
@@ -1246,9 +1656,16 @@
       <c r="G50" s="3" t="n"/>
       <c r="H50" s="3" t="n"/>
       <c r="I50" s="3" t="n"/>
+      <c r="J50" s="3" t="n"/>
+      <c r="K50" s="3" t="n"/>
+      <c r="L50" s="3" t="n"/>
+      <c r="M50" s="3" t="n"/>
+      <c r="N50" s="3" t="n"/>
+      <c r="O50" s="3" t="n"/>
+      <c r="P50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="n"/>
@@ -1259,9 +1676,16 @@
       <c r="G51" s="3" t="n"/>
       <c r="H51" s="3" t="n"/>
       <c r="I51" s="3" t="n"/>
+      <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="n"/>
+      <c r="L51" s="3" t="n"/>
+      <c r="M51" s="3" t="n"/>
+      <c r="N51" s="3" t="n"/>
+      <c r="O51" s="3" t="n"/>
+      <c r="P51" s="3" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="n"/>
@@ -1272,9 +1696,16 @@
       <c r="G52" s="3" t="n"/>
       <c r="H52" s="3" t="n"/>
       <c r="I52" s="3" t="n"/>
+      <c r="J52" s="3" t="n"/>
+      <c r="K52" s="3" t="n"/>
+      <c r="L52" s="3" t="n"/>
+      <c r="M52" s="3" t="n"/>
+      <c r="N52" s="3" t="n"/>
+      <c r="O52" s="3" t="n"/>
+      <c r="P52" s="3" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="n"/>
@@ -1285,9 +1716,16 @@
       <c r="G53" s="3" t="n"/>
       <c r="H53" s="3" t="n"/>
       <c r="I53" s="3" t="n"/>
+      <c r="J53" s="3" t="n"/>
+      <c r="K53" s="3" t="n"/>
+      <c r="L53" s="3" t="n"/>
+      <c r="M53" s="3" t="n"/>
+      <c r="N53" s="3" t="n"/>
+      <c r="O53" s="3" t="n"/>
+      <c r="P53" s="3" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="n"/>
@@ -1298,9 +1736,16 @@
       <c r="G54" s="3" t="n"/>
       <c r="H54" s="3" t="n"/>
       <c r="I54" s="3" t="n"/>
+      <c r="J54" s="3" t="n"/>
+      <c r="K54" s="3" t="n"/>
+      <c r="L54" s="3" t="n"/>
+      <c r="M54" s="3" t="n"/>
+      <c r="N54" s="3" t="n"/>
+      <c r="O54" s="3" t="n"/>
+      <c r="P54" s="3" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="n"/>
@@ -1311,9 +1756,16 @@
       <c r="G55" s="3" t="n"/>
       <c r="H55" s="3" t="n"/>
       <c r="I55" s="3" t="n"/>
+      <c r="J55" s="3" t="n"/>
+      <c r="K55" s="3" t="n"/>
+      <c r="L55" s="3" t="n"/>
+      <c r="M55" s="3" t="n"/>
+      <c r="N55" s="3" t="n"/>
+      <c r="O55" s="3" t="n"/>
+      <c r="P55" s="3" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="n"/>
@@ -1324,9 +1776,16 @@
       <c r="G56" s="3" t="n"/>
       <c r="H56" s="3" t="n"/>
       <c r="I56" s="3" t="n"/>
+      <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="n"/>
+      <c r="L56" s="3" t="n"/>
+      <c r="M56" s="3" t="n"/>
+      <c r="N56" s="3" t="n"/>
+      <c r="O56" s="3" t="n"/>
+      <c r="P56" s="3" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="n"/>
@@ -1337,9 +1796,16 @@
       <c r="G57" s="3" t="n"/>
       <c r="H57" s="3" t="n"/>
       <c r="I57" s="3" t="n"/>
+      <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="n"/>
+      <c r="L57" s="3" t="n"/>
+      <c r="M57" s="3" t="n"/>
+      <c r="N57" s="3" t="n"/>
+      <c r="O57" s="3" t="n"/>
+      <c r="P57" s="3" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="n"/>
@@ -1350,9 +1816,16 @@
       <c r="G58" s="3" t="n"/>
       <c r="H58" s="3" t="n"/>
       <c r="I58" s="3" t="n"/>
+      <c r="J58" s="3" t="n"/>
+      <c r="K58" s="3" t="n"/>
+      <c r="L58" s="3" t="n"/>
+      <c r="M58" s="3" t="n"/>
+      <c r="N58" s="3" t="n"/>
+      <c r="O58" s="3" t="n"/>
+      <c r="P58" s="3" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="n"/>
@@ -1363,9 +1836,16 @@
       <c r="G59" s="3" t="n"/>
       <c r="H59" s="3" t="n"/>
       <c r="I59" s="3" t="n"/>
+      <c r="J59" s="3" t="n"/>
+      <c r="K59" s="3" t="n"/>
+      <c r="L59" s="3" t="n"/>
+      <c r="M59" s="3" t="n"/>
+      <c r="N59" s="3" t="n"/>
+      <c r="O59" s="3" t="n"/>
+      <c r="P59" s="3" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="n"/>
@@ -1376,9 +1856,16 @@
       <c r="G60" s="3" t="n"/>
       <c r="H60" s="3" t="n"/>
       <c r="I60" s="3" t="n"/>
+      <c r="J60" s="3" t="n"/>
+      <c r="K60" s="3" t="n"/>
+      <c r="L60" s="3" t="n"/>
+      <c r="M60" s="3" t="n"/>
+      <c r="N60" s="3" t="n"/>
+      <c r="O60" s="3" t="n"/>
+      <c r="P60" s="3" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="n"/>
@@ -1389,9 +1876,16 @@
       <c r="G61" s="3" t="n"/>
       <c r="H61" s="3" t="n"/>
       <c r="I61" s="3" t="n"/>
+      <c r="J61" s="3" t="n"/>
+      <c r="K61" s="3" t="n"/>
+      <c r="L61" s="3" t="n"/>
+      <c r="M61" s="3" t="n"/>
+      <c r="N61" s="3" t="n"/>
+      <c r="O61" s="3" t="n"/>
+      <c r="P61" s="3" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="n"/>
@@ -1402,9 +1896,16 @@
       <c r="G62" s="3" t="n"/>
       <c r="H62" s="3" t="n"/>
       <c r="I62" s="3" t="n"/>
+      <c r="J62" s="3" t="n"/>
+      <c r="K62" s="3" t="n"/>
+      <c r="L62" s="3" t="n"/>
+      <c r="M62" s="3" t="n"/>
+      <c r="N62" s="3" t="n"/>
+      <c r="O62" s="3" t="n"/>
+      <c r="P62" s="3" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="n"/>
@@ -1415,9 +1916,16 @@
       <c r="G63" s="3" t="n"/>
       <c r="H63" s="3" t="n"/>
       <c r="I63" s="3" t="n"/>
+      <c r="J63" s="3" t="n"/>
+      <c r="K63" s="3" t="n"/>
+      <c r="L63" s="3" t="n"/>
+      <c r="M63" s="3" t="n"/>
+      <c r="N63" s="3" t="n"/>
+      <c r="O63" s="3" t="n"/>
+      <c r="P63" s="3" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="n"/>
@@ -1428,9 +1936,16 @@
       <c r="G64" s="3" t="n"/>
       <c r="H64" s="3" t="n"/>
       <c r="I64" s="3" t="n"/>
+      <c r="J64" s="3" t="n"/>
+      <c r="K64" s="3" t="n"/>
+      <c r="L64" s="3" t="n"/>
+      <c r="M64" s="3" t="n"/>
+      <c r="N64" s="3" t="n"/>
+      <c r="O64" s="3" t="n"/>
+      <c r="P64" s="3" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="n"/>
@@ -1441,9 +1956,16 @@
       <c r="G65" s="3" t="n"/>
       <c r="H65" s="3" t="n"/>
       <c r="I65" s="3" t="n"/>
+      <c r="J65" s="3" t="n"/>
+      <c r="K65" s="3" t="n"/>
+      <c r="L65" s="3" t="n"/>
+      <c r="M65" s="3" t="n"/>
+      <c r="N65" s="3" t="n"/>
+      <c r="O65" s="3" t="n"/>
+      <c r="P65" s="3" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>65</v>
       </c>
       <c r="B66" s="3" t="n"/>
@@ -1454,9 +1976,16 @@
       <c r="G66" s="3" t="n"/>
       <c r="H66" s="3" t="n"/>
       <c r="I66" s="3" t="n"/>
+      <c r="J66" s="3" t="n"/>
+      <c r="K66" s="3" t="n"/>
+      <c r="L66" s="3" t="n"/>
+      <c r="M66" s="3" t="n"/>
+      <c r="N66" s="3" t="n"/>
+      <c r="O66" s="3" t="n"/>
+      <c r="P66" s="3" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="3" t="n"/>
@@ -1467,9 +1996,16 @@
       <c r="G67" s="3" t="n"/>
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="3" t="n"/>
+      <c r="J67" s="3" t="n"/>
+      <c r="K67" s="3" t="n"/>
+      <c r="L67" s="3" t="n"/>
+      <c r="M67" s="3" t="n"/>
+      <c r="N67" s="3" t="n"/>
+      <c r="O67" s="3" t="n"/>
+      <c r="P67" s="3" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>67</v>
       </c>
       <c r="B68" s="3" t="n"/>
@@ -1480,9 +2016,16 @@
       <c r="G68" s="3" t="n"/>
       <c r="H68" s="3" t="n"/>
       <c r="I68" s="3" t="n"/>
+      <c r="J68" s="3" t="n"/>
+      <c r="K68" s="3" t="n"/>
+      <c r="L68" s="3" t="n"/>
+      <c r="M68" s="3" t="n"/>
+      <c r="N68" s="3" t="n"/>
+      <c r="O68" s="3" t="n"/>
+      <c r="P68" s="3" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="3" t="n"/>
@@ -1493,9 +2036,16 @@
       <c r="G69" s="3" t="n"/>
       <c r="H69" s="3" t="n"/>
       <c r="I69" s="3" t="n"/>
+      <c r="J69" s="3" t="n"/>
+      <c r="K69" s="3" t="n"/>
+      <c r="L69" s="3" t="n"/>
+      <c r="M69" s="3" t="n"/>
+      <c r="N69" s="3" t="n"/>
+      <c r="O69" s="3" t="n"/>
+      <c r="P69" s="3" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="3" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="n"/>
@@ -1506,9 +2056,16 @@
       <c r="G70" s="3" t="n"/>
       <c r="H70" s="3" t="n"/>
       <c r="I70" s="3" t="n"/>
+      <c r="J70" s="3" t="n"/>
+      <c r="K70" s="3" t="n"/>
+      <c r="L70" s="3" t="n"/>
+      <c r="M70" s="3" t="n"/>
+      <c r="N70" s="3" t="n"/>
+      <c r="O70" s="3" t="n"/>
+      <c r="P70" s="3" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="3" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="n"/>
@@ -1519,9 +2076,16 @@
       <c r="G71" s="3" t="n"/>
       <c r="H71" s="3" t="n"/>
       <c r="I71" s="3" t="n"/>
+      <c r="J71" s="3" t="n"/>
+      <c r="K71" s="3" t="n"/>
+      <c r="L71" s="3" t="n"/>
+      <c r="M71" s="3" t="n"/>
+      <c r="N71" s="3" t="n"/>
+      <c r="O71" s="3" t="n"/>
+      <c r="P71" s="3" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="3" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="n"/>
@@ -1532,9 +2096,16 @@
       <c r="G72" s="3" t="n"/>
       <c r="H72" s="3" t="n"/>
       <c r="I72" s="3" t="n"/>
+      <c r="J72" s="3" t="n"/>
+      <c r="K72" s="3" t="n"/>
+      <c r="L72" s="3" t="n"/>
+      <c r="M72" s="3" t="n"/>
+      <c r="N72" s="3" t="n"/>
+      <c r="O72" s="3" t="n"/>
+      <c r="P72" s="3" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="3" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="3" t="n"/>
@@ -1545,9 +2116,16 @@
       <c r="G73" s="3" t="n"/>
       <c r="H73" s="3" t="n"/>
       <c r="I73" s="3" t="n"/>
+      <c r="J73" s="3" t="n"/>
+      <c r="K73" s="3" t="n"/>
+      <c r="L73" s="3" t="n"/>
+      <c r="M73" s="3" t="n"/>
+      <c r="N73" s="3" t="n"/>
+      <c r="O73" s="3" t="n"/>
+      <c r="P73" s="3" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="3" t="n">
         <v>73</v>
       </c>
       <c r="B74" s="3" t="n"/>
@@ -1558,9 +2136,16 @@
       <c r="G74" s="3" t="n"/>
       <c r="H74" s="3" t="n"/>
       <c r="I74" s="3" t="n"/>
+      <c r="J74" s="3" t="n"/>
+      <c r="K74" s="3" t="n"/>
+      <c r="L74" s="3" t="n"/>
+      <c r="M74" s="3" t="n"/>
+      <c r="N74" s="3" t="n"/>
+      <c r="O74" s="3" t="n"/>
+      <c r="P74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="3" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="3" t="n"/>
@@ -1571,9 +2156,16 @@
       <c r="G75" s="3" t="n"/>
       <c r="H75" s="3" t="n"/>
       <c r="I75" s="3" t="n"/>
+      <c r="J75" s="3" t="n"/>
+      <c r="K75" s="3" t="n"/>
+      <c r="L75" s="3" t="n"/>
+      <c r="M75" s="3" t="n"/>
+      <c r="N75" s="3" t="n"/>
+      <c r="O75" s="3" t="n"/>
+      <c r="P75" s="3" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="3" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="3" t="n"/>
@@ -1584,9 +2176,16 @@
       <c r="G76" s="3" t="n"/>
       <c r="H76" s="3" t="n"/>
       <c r="I76" s="3" t="n"/>
+      <c r="J76" s="3" t="n"/>
+      <c r="K76" s="3" t="n"/>
+      <c r="L76" s="3" t="n"/>
+      <c r="M76" s="3" t="n"/>
+      <c r="N76" s="3" t="n"/>
+      <c r="O76" s="3" t="n"/>
+      <c r="P76" s="3" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="3" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="3" t="n"/>
@@ -1597,9 +2196,16 @@
       <c r="G77" s="3" t="n"/>
       <c r="H77" s="3" t="n"/>
       <c r="I77" s="3" t="n"/>
+      <c r="J77" s="3" t="n"/>
+      <c r="K77" s="3" t="n"/>
+      <c r="L77" s="3" t="n"/>
+      <c r="M77" s="3" t="n"/>
+      <c r="N77" s="3" t="n"/>
+      <c r="O77" s="3" t="n"/>
+      <c r="P77" s="3" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="3" t="n">
         <v>77</v>
       </c>
       <c r="B78" s="3" t="n"/>
@@ -1610,9 +2216,16 @@
       <c r="G78" s="3" t="n"/>
       <c r="H78" s="3" t="n"/>
       <c r="I78" s="3" t="n"/>
+      <c r="J78" s="3" t="n"/>
+      <c r="K78" s="3" t="n"/>
+      <c r="L78" s="3" t="n"/>
+      <c r="M78" s="3" t="n"/>
+      <c r="N78" s="3" t="n"/>
+      <c r="O78" s="3" t="n"/>
+      <c r="P78" s="3" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="3" t="n">
         <v>78</v>
       </c>
       <c r="B79" s="3" t="n"/>
@@ -1623,9 +2236,16 @@
       <c r="G79" s="3" t="n"/>
       <c r="H79" s="3" t="n"/>
       <c r="I79" s="3" t="n"/>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="n"/>
+      <c r="L79" s="3" t="n"/>
+      <c r="M79" s="3" t="n"/>
+      <c r="N79" s="3" t="n"/>
+      <c r="O79" s="3" t="n"/>
+      <c r="P79" s="3" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="3" t="n">
         <v>79</v>
       </c>
       <c r="B80" s="3" t="n"/>
@@ -1636,9 +2256,16 @@
       <c r="G80" s="3" t="n"/>
       <c r="H80" s="3" t="n"/>
       <c r="I80" s="3" t="n"/>
+      <c r="J80" s="3" t="n"/>
+      <c r="K80" s="3" t="n"/>
+      <c r="L80" s="3" t="n"/>
+      <c r="M80" s="3" t="n"/>
+      <c r="N80" s="3" t="n"/>
+      <c r="O80" s="3" t="n"/>
+      <c r="P80" s="3" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="3" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="3" t="n"/>
@@ -1649,9 +2276,16 @@
       <c r="G81" s="3" t="n"/>
       <c r="H81" s="3" t="n"/>
       <c r="I81" s="3" t="n"/>
+      <c r="J81" s="3" t="n"/>
+      <c r="K81" s="3" t="n"/>
+      <c r="L81" s="3" t="n"/>
+      <c r="M81" s="3" t="n"/>
+      <c r="N81" s="3" t="n"/>
+      <c r="O81" s="3" t="n"/>
+      <c r="P81" s="3" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="3" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="3" t="n"/>
@@ -1662,9 +2296,16 @@
       <c r="G82" s="3" t="n"/>
       <c r="H82" s="3" t="n"/>
       <c r="I82" s="3" t="n"/>
+      <c r="J82" s="3" t="n"/>
+      <c r="K82" s="3" t="n"/>
+      <c r="L82" s="3" t="n"/>
+      <c r="M82" s="3" t="n"/>
+      <c r="N82" s="3" t="n"/>
+      <c r="O82" s="3" t="n"/>
+      <c r="P82" s="3" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="3" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="n"/>
@@ -1675,9 +2316,16 @@
       <c r="G83" s="3" t="n"/>
       <c r="H83" s="3" t="n"/>
       <c r="I83" s="3" t="n"/>
+      <c r="J83" s="3" t="n"/>
+      <c r="K83" s="3" t="n"/>
+      <c r="L83" s="3" t="n"/>
+      <c r="M83" s="3" t="n"/>
+      <c r="N83" s="3" t="n"/>
+      <c r="O83" s="3" t="n"/>
+      <c r="P83" s="3" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="3" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="n"/>
@@ -1688,9 +2336,16 @@
       <c r="G84" s="3" t="n"/>
       <c r="H84" s="3" t="n"/>
       <c r="I84" s="3" t="n"/>
+      <c r="J84" s="3" t="n"/>
+      <c r="K84" s="3" t="n"/>
+      <c r="L84" s="3" t="n"/>
+      <c r="M84" s="3" t="n"/>
+      <c r="N84" s="3" t="n"/>
+      <c r="O84" s="3" t="n"/>
+      <c r="P84" s="3" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="3" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="n"/>
@@ -1701,9 +2356,16 @@
       <c r="G85" s="3" t="n"/>
       <c r="H85" s="3" t="n"/>
       <c r="I85" s="3" t="n"/>
+      <c r="J85" s="3" t="n"/>
+      <c r="K85" s="3" t="n"/>
+      <c r="L85" s="3" t="n"/>
+      <c r="M85" s="3" t="n"/>
+      <c r="N85" s="3" t="n"/>
+      <c r="O85" s="3" t="n"/>
+      <c r="P85" s="3" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="3" t="n">
         <v>85</v>
       </c>
       <c r="B86" s="3" t="n"/>
@@ -1714,9 +2376,16 @@
       <c r="G86" s="3" t="n"/>
       <c r="H86" s="3" t="n"/>
       <c r="I86" s="3" t="n"/>
+      <c r="J86" s="3" t="n"/>
+      <c r="K86" s="3" t="n"/>
+      <c r="L86" s="3" t="n"/>
+      <c r="M86" s="3" t="n"/>
+      <c r="N86" s="3" t="n"/>
+      <c r="O86" s="3" t="n"/>
+      <c r="P86" s="3" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="3" t="n">
         <v>86</v>
       </c>
       <c r="B87" s="3" t="n"/>
@@ -1727,9 +2396,16 @@
       <c r="G87" s="3" t="n"/>
       <c r="H87" s="3" t="n"/>
       <c r="I87" s="3" t="n"/>
+      <c r="J87" s="3" t="n"/>
+      <c r="K87" s="3" t="n"/>
+      <c r="L87" s="3" t="n"/>
+      <c r="M87" s="3" t="n"/>
+      <c r="N87" s="3" t="n"/>
+      <c r="O87" s="3" t="n"/>
+      <c r="P87" s="3" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="3" t="n">
         <v>87</v>
       </c>
       <c r="B88" s="3" t="n"/>
@@ -1740,9 +2416,16 @@
       <c r="G88" s="3" t="n"/>
       <c r="H88" s="3" t="n"/>
       <c r="I88" s="3" t="n"/>
+      <c r="J88" s="3" t="n"/>
+      <c r="K88" s="3" t="n"/>
+      <c r="L88" s="3" t="n"/>
+      <c r="M88" s="3" t="n"/>
+      <c r="N88" s="3" t="n"/>
+      <c r="O88" s="3" t="n"/>
+      <c r="P88" s="3" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="3" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="3" t="n"/>
@@ -1753,9 +2436,16 @@
       <c r="G89" s="3" t="n"/>
       <c r="H89" s="3" t="n"/>
       <c r="I89" s="3" t="n"/>
+      <c r="J89" s="3" t="n"/>
+      <c r="K89" s="3" t="n"/>
+      <c r="L89" s="3" t="n"/>
+      <c r="M89" s="3" t="n"/>
+      <c r="N89" s="3" t="n"/>
+      <c r="O89" s="3" t="n"/>
+      <c r="P89" s="3" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="3" t="n">
         <v>89</v>
       </c>
       <c r="B90" s="3" t="n"/>
@@ -1766,9 +2456,16 @@
       <c r="G90" s="3" t="n"/>
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="3" t="n"/>
+      <c r="J90" s="3" t="n"/>
+      <c r="K90" s="3" t="n"/>
+      <c r="L90" s="3" t="n"/>
+      <c r="M90" s="3" t="n"/>
+      <c r="N90" s="3" t="n"/>
+      <c r="O90" s="3" t="n"/>
+      <c r="P90" s="3" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="3" t="n">
         <v>90</v>
       </c>
       <c r="B91" s="3" t="n"/>
@@ -1779,9 +2476,16 @@
       <c r="G91" s="3" t="n"/>
       <c r="H91" s="3" t="n"/>
       <c r="I91" s="3" t="n"/>
+      <c r="J91" s="3" t="n"/>
+      <c r="K91" s="3" t="n"/>
+      <c r="L91" s="3" t="n"/>
+      <c r="M91" s="3" t="n"/>
+      <c r="N91" s="3" t="n"/>
+      <c r="O91" s="3" t="n"/>
+      <c r="P91" s="3" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="3" t="n">
         <v>91</v>
       </c>
       <c r="B92" s="3" t="n"/>
@@ -1792,9 +2496,16 @@
       <c r="G92" s="3" t="n"/>
       <c r="H92" s="3" t="n"/>
       <c r="I92" s="3" t="n"/>
+      <c r="J92" s="3" t="n"/>
+      <c r="K92" s="3" t="n"/>
+      <c r="L92" s="3" t="n"/>
+      <c r="M92" s="3" t="n"/>
+      <c r="N92" s="3" t="n"/>
+      <c r="O92" s="3" t="n"/>
+      <c r="P92" s="3" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="3" t="n">
         <v>92</v>
       </c>
       <c r="B93" s="3" t="n"/>
@@ -1805,9 +2516,16 @@
       <c r="G93" s="3" t="n"/>
       <c r="H93" s="3" t="n"/>
       <c r="I93" s="3" t="n"/>
+      <c r="J93" s="3" t="n"/>
+      <c r="K93" s="3" t="n"/>
+      <c r="L93" s="3" t="n"/>
+      <c r="M93" s="3" t="n"/>
+      <c r="N93" s="3" t="n"/>
+      <c r="O93" s="3" t="n"/>
+      <c r="P93" s="3" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="3" t="n">
         <v>93</v>
       </c>
       <c r="B94" s="3" t="n"/>
@@ -1818,9 +2536,16 @@
       <c r="G94" s="3" t="n"/>
       <c r="H94" s="3" t="n"/>
       <c r="I94" s="3" t="n"/>
+      <c r="J94" s="3" t="n"/>
+      <c r="K94" s="3" t="n"/>
+      <c r="L94" s="3" t="n"/>
+      <c r="M94" s="3" t="n"/>
+      <c r="N94" s="3" t="n"/>
+      <c r="O94" s="3" t="n"/>
+      <c r="P94" s="3" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="3" t="n">
         <v>94</v>
       </c>
       <c r="B95" s="3" t="n"/>
@@ -1831,9 +2556,16 @@
       <c r="G95" s="3" t="n"/>
       <c r="H95" s="3" t="n"/>
       <c r="I95" s="3" t="n"/>
+      <c r="J95" s="3" t="n"/>
+      <c r="K95" s="3" t="n"/>
+      <c r="L95" s="3" t="n"/>
+      <c r="M95" s="3" t="n"/>
+      <c r="N95" s="3" t="n"/>
+      <c r="O95" s="3" t="n"/>
+      <c r="P95" s="3" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="3" t="n">
         <v>95</v>
       </c>
       <c r="B96" s="3" t="n"/>
@@ -1844,9 +2576,16 @@
       <c r="G96" s="3" t="n"/>
       <c r="H96" s="3" t="n"/>
       <c r="I96" s="3" t="n"/>
+      <c r="J96" s="3" t="n"/>
+      <c r="K96" s="3" t="n"/>
+      <c r="L96" s="3" t="n"/>
+      <c r="M96" s="3" t="n"/>
+      <c r="N96" s="3" t="n"/>
+      <c r="O96" s="3" t="n"/>
+      <c r="P96" s="3" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="3" t="n">
         <v>96</v>
       </c>
       <c r="B97" s="3" t="n"/>
@@ -1857,9 +2596,16 @@
       <c r="G97" s="3" t="n"/>
       <c r="H97" s="3" t="n"/>
       <c r="I97" s="3" t="n"/>
+      <c r="J97" s="3" t="n"/>
+      <c r="K97" s="3" t="n"/>
+      <c r="L97" s="3" t="n"/>
+      <c r="M97" s="3" t="n"/>
+      <c r="N97" s="3" t="n"/>
+      <c r="O97" s="3" t="n"/>
+      <c r="P97" s="3" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="3" t="n">
         <v>97</v>
       </c>
       <c r="B98" s="3" t="n"/>
@@ -1870,9 +2616,16 @@
       <c r="G98" s="3" t="n"/>
       <c r="H98" s="3" t="n"/>
       <c r="I98" s="3" t="n"/>
+      <c r="J98" s="3" t="n"/>
+      <c r="K98" s="3" t="n"/>
+      <c r="L98" s="3" t="n"/>
+      <c r="M98" s="3" t="n"/>
+      <c r="N98" s="3" t="n"/>
+      <c r="O98" s="3" t="n"/>
+      <c r="P98" s="3" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="3" t="n">
         <v>98</v>
       </c>
       <c r="B99" s="3" t="n"/>
@@ -1883,9 +2636,16 @@
       <c r="G99" s="3" t="n"/>
       <c r="H99" s="3" t="n"/>
       <c r="I99" s="3" t="n"/>
+      <c r="J99" s="3" t="n"/>
+      <c r="K99" s="3" t="n"/>
+      <c r="L99" s="3" t="n"/>
+      <c r="M99" s="3" t="n"/>
+      <c r="N99" s="3" t="n"/>
+      <c r="O99" s="3" t="n"/>
+      <c r="P99" s="3" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="3" t="n">
         <v>99</v>
       </c>
       <c r="B100" s="3" t="n"/>
@@ -1896,6 +2656,13 @@
       <c r="G100" s="3" t="n"/>
       <c r="H100" s="3" t="n"/>
       <c r="I100" s="3" t="n"/>
+      <c r="J100" s="3" t="n"/>
+      <c r="K100" s="3" t="n"/>
+      <c r="L100" s="3" t="n"/>
+      <c r="M100" s="3" t="n"/>
+      <c r="N100" s="3" t="n"/>
+      <c r="O100" s="3" t="n"/>
+      <c r="P100" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1908,11 +2675,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1921,11 +2688,6 @@
           <t>【受講者一覧 入力説明】</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1959,125 +2721,204 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>受講者の氏名を入力（例：山田 太郎）</t>
+          <t>受講者の氏名を入力（例：山田 太郎、姓と名の間に全角スペース）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>雇用保険被保険者番号</t>
+          <t>フリガナ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11桁のハイフン区切り形式で入力（例：1234-567890-1）</t>
+          <t>全角カタカナで入力（例：ヤマダ タロウ）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>雇用形態</t>
+          <t>性別</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>「正規雇用」または「有期契約」を選択</t>
+          <t>「男」または「女」を入力（男女別の人数集計に使用されます）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>カリキュラム名</t>
+          <t>メールアドレス</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>受講する研修・カリキュラムの名称</t>
+          <t>eラーニング訓練の場合は必須</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>訓練開始日</t>
+          <t>雇用区分</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YYYY/MM/DD形式で入力（例：2026/05/01）</t>
+          <t>「正規雇用労働者等」または「有期契約労働者等」</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>訓練終了日</t>
+          <t>雇用保険被保険者番号</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YYYY/MM/DD形式で入力（例：2026/07/31）</t>
+          <t>11桁のハイフン区切り形式（例：1234-567890-1）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>受講料(税抜)</t>
+          <t>所属事業所</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>税抜金額を数値で入力</t>
+          <t>本社以外の事業所の場合は事業所名を入力</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>助成コース</t>
+          <t>受講場所(在宅の場合)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>「リスキリング」または「定額制」を選択</t>
+          <t>在宅で受講する場合に「在宅」と入力</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>受講場所(名称・住所)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>在宅以外の場合は受講場所の名称・住所を入力</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【助成コースについて】</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>雇用契約書チェック</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>雇用契約書を確認したかチェック（例：有/無）</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>リスキリング</t>
+          <t>カリキュラム名</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>事業展開等リスキリング支援コース - DX化・グリーン化に伴う訓練向け</t>
+          <t>受講する研修・カリキュラムの名称</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>訓練開始日</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>YYYY/MM/DD形式（例：2026/05/01）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>訓練終了日</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>YYYY/MM/DD形式（例：2026/07/31）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>受講料(税抜)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>税抜金額を数値で入力</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>助成コース</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>「リスキリング」または「定額制」</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>【助成コースについて】</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>リスキリング</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>事業展開等リスキリング支援コース</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>定額制</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>人への投資促進コース（定額制訓練） - サブスク型e-ラーニング向け</t>
         </is>

--- a/templates/受講者一覧_入力テンプレート.xlsx
+++ b/templates/受講者一覧_入力テンプレート.xlsx
@@ -485,10 +485,10 @@
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
@@ -576,7 +576,8 @@
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>助成コース
-(リスキリング/定額制)</t>
+(e-ラーニング/インタラクティブ(通学制)/
+インタラクティブ(同時双方向)/定額制)</t>
         </is>
       </c>
     </row>
@@ -646,7 +647,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>リスキリング</t>
+          <t>e-ラーニング</t>
         </is>
       </c>
     </row>
@@ -720,7 +721,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>リスキリング</t>
+          <t>インタラクティブ（通学制）</t>
         </is>
       </c>
     </row>
@@ -2665,6 +2666,17 @@
       <c r="P100" s="3" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="P2:P100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"e-ラーニング,インタラクティブ（通学制）,インタラクティブ（同時双方向）,定額制"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"男,女"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"正規雇用労働者等,有期契約労働者等"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2675,11 +2687,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2745,7 +2757,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>「男」または「女」を入力（男女別の人数集計に使用されます）</t>
+          <t>「男」または「女」を入力（男女別の人数集計に使用）</t>
         </is>
       </c>
     </row>
@@ -2889,38 +2901,62 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>「リスキリング」または「定額制」</t>
+          <t>下記4種から選択（プルダウン）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>【助成コースについて】</t>
+          <t>【助成コースの種類】</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>リスキリング</t>
+          <t>e-ラーニング</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>事業展開等リスキリング支援コース</t>
+          <t>非同期型のeラーニング訓練 → 様式1-1号 12 の③eラーニングに自動チェック</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>インタラクティブ（通学制）</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>対面型の通学訓練 → 様式1-1号 12 の①通学制に自動チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>インタラクティブ（同時双方向）</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>同時双方向型のオンライン訓練 → 様式1-1号 12 の②同時双方向に自動チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>定額制</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>人への投資促進コース（定額制訓練） - サブスク型e-ラーニング向け</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>定額制サービスによる訓練（人への投資促進コース） → 様式1-1号 12 の③eラーニングに自動チェック</t>
         </is>
       </c>
     </row>
